--- a/results/val/multiClass_AD_results.xlsx
+++ b/results/val/multiClass_AD_results.xlsx
@@ -566,49 +566,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.407</v>
+        <v>0.48572</v>
       </c>
       <c r="C2" t="n">
-        <v>0.399</v>
+        <v>0.43403</v>
       </c>
       <c r="D2" t="n">
-        <v>0.415</v>
+        <v>0.5514</v>
       </c>
       <c r="E2" t="n">
-        <v>0.581</v>
+        <v>0.65566</v>
       </c>
       <c r="F2" t="n">
-        <v>0.439</v>
+        <v>0.54288</v>
       </c>
       <c r="G2" t="n">
-        <v>0.861</v>
+        <v>0.82759</v>
       </c>
       <c r="H2" t="n">
-        <v>0.745</v>
+        <v>0.57973</v>
       </c>
       <c r="I2" t="n">
-        <v>0.594</v>
+        <v>0.40819</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.823</v>
+        <v>0.8283199999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.912</v>
+        <v>0.92492</v>
       </c>
       <c r="M2" t="n">
         <v>0.75</v>
       </c>
       <c r="N2" t="n">
-        <v>0.255</v>
+        <v>0.23635</v>
       </c>
       <c r="O2" t="n">
-        <v>0.168</v>
+        <v>0.15141</v>
       </c>
       <c r="P2" t="n">
-        <v>0.528</v>
+        <v>0.53846</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -629,10 +629,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.284</v>
+        <v>0.24824</v>
       </c>
       <c r="X2" t="n">
-        <v>0.488</v>
+        <v>0.32716</v>
       </c>
       <c r="Y2" t="n">
         <v>0.2</v>
@@ -645,49 +645,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.392</v>
+        <v>0.50234</v>
       </c>
       <c r="C3" t="n">
-        <v>0.39</v>
+        <v>0.46805</v>
       </c>
       <c r="D3" t="n">
-        <v>0.395</v>
+        <v>0.54206</v>
       </c>
       <c r="E3" t="n">
-        <v>0.547</v>
+        <v>0.65522</v>
       </c>
       <c r="F3" t="n">
-        <v>0.401</v>
+        <v>0.54228</v>
       </c>
       <c r="G3" t="n">
-        <v>0.861</v>
+        <v>0.82759</v>
       </c>
       <c r="H3" t="n">
-        <v>0.705</v>
+        <v>0.61396</v>
       </c>
       <c r="I3" t="n">
-        <v>0.544</v>
+        <v>0.44296</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.81942</v>
       </c>
       <c r="L3" t="n">
-        <v>0.887</v>
+        <v>0.90301</v>
       </c>
       <c r="M3" t="n">
         <v>0.75</v>
       </c>
       <c r="N3" t="n">
-        <v>0.177</v>
+        <v>0.2225</v>
       </c>
       <c r="O3" t="n">
-        <v>0.117</v>
+        <v>0.14309</v>
       </c>
       <c r="P3" t="n">
-        <v>0.361</v>
+        <v>0.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.276</v>
+        <v>0.27586</v>
       </c>
       <c r="X3" t="n">
-        <v>0.444</v>
+        <v>0.44444</v>
       </c>
       <c r="Y3" t="n">
         <v>0.2</v>
@@ -724,49 +724,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.432</v>
+        <v>0.54008</v>
       </c>
       <c r="C4" t="n">
-        <v>0.434</v>
+        <v>0.52089</v>
       </c>
       <c r="D4" t="n">
-        <v>0.43</v>
+        <v>0.56075</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.84193</v>
       </c>
       <c r="F4" t="n">
-        <v>0.526</v>
+        <v>0.72701</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.555</v>
+        <v>0.5554</v>
       </c>
       <c r="I4" t="n">
-        <v>0.454</v>
+        <v>0.45433</v>
       </c>
       <c r="J4" t="n">
-        <v>0.714</v>
+        <v>0.71429</v>
       </c>
       <c r="K4" t="n">
-        <v>0.617</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.79488</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5625</v>
       </c>
       <c r="N4" t="n">
-        <v>0.239</v>
+        <v>0.22899</v>
       </c>
       <c r="O4" t="n">
-        <v>0.16</v>
+        <v>0.15227</v>
       </c>
       <c r="P4" t="n">
-        <v>0.472</v>
+        <v>0.46154</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.591</v>
+        <v>0.51156</v>
       </c>
       <c r="X4" t="n">
-        <v>0.723</v>
+        <v>0.52366</v>
       </c>
       <c r="Y4" t="n">
         <v>0.5</v>
@@ -803,49 +803,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.413</v>
+        <v>0.53146</v>
       </c>
       <c r="C5" t="n">
-        <v>0.434</v>
+        <v>0.52127</v>
       </c>
       <c r="D5" t="n">
-        <v>0.395</v>
+        <v>0.54206</v>
       </c>
       <c r="E5" t="n">
-        <v>0.572</v>
+        <v>0.79488</v>
       </c>
       <c r="F5" t="n">
-        <v>0.401</v>
+        <v>0.65959</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.466</v>
+        <v>0.4662</v>
       </c>
       <c r="I5" t="n">
-        <v>0.394</v>
+        <v>0.3937</v>
       </c>
       <c r="J5" t="n">
-        <v>0.571</v>
+        <v>0.57143</v>
       </c>
       <c r="K5" t="n">
-        <v>0.639</v>
+        <v>0.62414</v>
       </c>
       <c r="L5" t="n">
-        <v>0.887</v>
+        <v>0.83027</v>
       </c>
       <c r="M5" t="n">
         <v>0.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.152</v>
+        <v>0.1926</v>
       </c>
       <c r="O5" t="n">
-        <v>0.101</v>
+        <v>0.12468</v>
       </c>
       <c r="P5" t="n">
-        <v>0.306</v>
+        <v>0.42308</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -857,19 +857,19 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.118</v>
+        <v>0.18182</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>0.062</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.579</v>
+        <v>0.51515</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="Y5" t="n">
         <v>0.5</v>
@@ -1023,49 +1023,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.373</v>
+        <v>0.45411</v>
       </c>
       <c r="C2" t="n">
-        <v>0.399</v>
+        <v>0.43403</v>
       </c>
       <c r="D2" t="n">
-        <v>0.35</v>
+        <v>0.47615</v>
       </c>
       <c r="E2" t="n">
-        <v>0.571</v>
+        <v>0.64367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.439</v>
+        <v>0.54288</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.7904099999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.707</v>
+        <v>0.55661</v>
       </c>
       <c r="I2" t="n">
-        <v>0.594</v>
+        <v>0.40819</v>
       </c>
       <c r="J2" t="n">
-        <v>0.875</v>
+        <v>0.87463</v>
       </c>
       <c r="K2" t="n">
-        <v>0.656</v>
+        <v>0.65901</v>
       </c>
       <c r="L2" t="n">
-        <v>0.912</v>
+        <v>0.92492</v>
       </c>
       <c r="M2" t="n">
-        <v>0.512</v>
+        <v>0.51186</v>
       </c>
       <c r="N2" t="n">
-        <v>0.245</v>
+        <v>0.22951</v>
       </c>
       <c r="O2" t="n">
-        <v>0.168</v>
+        <v>0.15141</v>
       </c>
       <c r="P2" t="n">
-        <v>0.449</v>
+        <v>0.47408</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1086,13 +1086,13 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.216</v>
+        <v>0.1949</v>
       </c>
       <c r="X2" t="n">
-        <v>0.488</v>
+        <v>0.32716</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.139</v>
+        <v>0.13879</v>
       </c>
     </row>
     <row r="3">
@@ -1102,49 +1102,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.353</v>
+        <v>0.4633</v>
       </c>
       <c r="C3" t="n">
-        <v>0.39</v>
+        <v>0.46805</v>
       </c>
       <c r="D3" t="n">
-        <v>0.323</v>
+        <v>0.45865</v>
       </c>
       <c r="E3" t="n">
-        <v>0.537</v>
+        <v>0.64255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.401</v>
+        <v>0.54228</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.78831</v>
       </c>
       <c r="H3" t="n">
-        <v>0.666</v>
+        <v>0.58404</v>
       </c>
       <c r="I3" t="n">
-        <v>0.544</v>
+        <v>0.44296</v>
       </c>
       <c r="J3" t="n">
-        <v>0.857</v>
+        <v>0.85701</v>
       </c>
       <c r="K3" t="n">
-        <v>0.642</v>
+        <v>0.64601</v>
       </c>
       <c r="L3" t="n">
-        <v>0.887</v>
+        <v>0.90301</v>
       </c>
       <c r="M3" t="n">
-        <v>0.503</v>
+        <v>0.50288</v>
       </c>
       <c r="N3" t="n">
-        <v>0.169</v>
+        <v>0.2142</v>
       </c>
       <c r="O3" t="n">
-        <v>0.117</v>
+        <v>0.14309</v>
       </c>
       <c r="P3" t="n">
-        <v>0.308</v>
+        <v>0.42586</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1165,13 +1165,13 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.176</v>
+        <v>0.17596</v>
       </c>
       <c r="X3" t="n">
-        <v>0.444</v>
+        <v>0.44444</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.11</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="4">
@@ -1181,49 +1181,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.376</v>
+        <v>0.49781</v>
       </c>
       <c r="C4" t="n">
-        <v>0.434</v>
+        <v>0.52089</v>
       </c>
       <c r="D4" t="n">
-        <v>0.331</v>
+        <v>0.47669</v>
       </c>
       <c r="E4" t="n">
-        <v>0.676</v>
+        <v>0.82238</v>
       </c>
       <c r="F4" t="n">
-        <v>0.526</v>
+        <v>0.72701</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.94654</v>
       </c>
       <c r="H4" t="n">
-        <v>0.502</v>
+        <v>0.50159</v>
       </c>
       <c r="I4" t="n">
-        <v>0.454</v>
+        <v>0.45433</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55981</v>
       </c>
       <c r="K4" t="n">
-        <v>0.465</v>
+        <v>0.48754</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.79488</v>
       </c>
       <c r="M4" t="n">
-        <v>0.352</v>
+        <v>0.3516</v>
       </c>
       <c r="N4" t="n">
-        <v>0.232</v>
+        <v>0.22538</v>
       </c>
       <c r="O4" t="n">
-        <v>0.16</v>
+        <v>0.15227</v>
       </c>
       <c r="P4" t="n">
-        <v>0.419</v>
+        <v>0.43352</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1244,13 +1244,13 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.397</v>
+        <v>0.35981</v>
       </c>
       <c r="X4" t="n">
-        <v>0.723</v>
+        <v>0.52366</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.274</v>
+        <v>0.27406</v>
       </c>
     </row>
     <row r="5">
@@ -1260,49 +1260,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.348</v>
+        <v>0.4851</v>
       </c>
       <c r="C5" t="n">
-        <v>0.434</v>
+        <v>0.52127</v>
       </c>
       <c r="D5" t="n">
-        <v>0.291</v>
+        <v>0.45362</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.77654</v>
       </c>
       <c r="F5" t="n">
-        <v>0.401</v>
+        <v>0.65959</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.94391</v>
       </c>
       <c r="H5" t="n">
-        <v>0.404</v>
+        <v>0.40445</v>
       </c>
       <c r="I5" t="n">
-        <v>0.394</v>
+        <v>0.3937</v>
       </c>
       <c r="J5" t="n">
-        <v>0.416</v>
+        <v>0.41581</v>
       </c>
       <c r="K5" t="n">
-        <v>0.493</v>
+        <v>0.48349</v>
       </c>
       <c r="L5" t="n">
-        <v>0.887</v>
+        <v>0.83027</v>
       </c>
       <c r="M5" t="n">
-        <v>0.341</v>
+        <v>0.34105</v>
       </c>
       <c r="N5" t="n">
-        <v>0.149</v>
+        <v>0.18879</v>
       </c>
       <c r="O5" t="n">
-        <v>0.101</v>
+        <v>0.12468</v>
       </c>
       <c r="P5" t="n">
-        <v>0.281</v>
+        <v>0.38862</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1314,22 +1314,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01</v>
+        <v>0.01653</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005</v>
+        <v>0.008330000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0.378</v>
+        <v>0.34996</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.261</v>
+        <v>0.26092</v>
       </c>
     </row>
   </sheetData>
@@ -1480,49 +1480,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.333</v>
+        <v>0.42138</v>
       </c>
       <c r="C2" t="n">
-        <v>0.399</v>
+        <v>0.43403</v>
       </c>
       <c r="D2" t="n">
-        <v>0.285</v>
+        <v>0.40944</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.63089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.439</v>
+        <v>0.54288</v>
       </c>
       <c r="G2" t="n">
-        <v>0.771</v>
+        <v>0.7529400000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.657</v>
+        <v>0.52494</v>
       </c>
       <c r="I2" t="n">
-        <v>0.594</v>
+        <v>0.40819</v>
       </c>
       <c r="J2" t="n">
-        <v>0.735</v>
+        <v>0.73524</v>
       </c>
       <c r="K2" t="n">
-        <v>0.462</v>
+        <v>0.46314</v>
       </c>
       <c r="L2" t="n">
-        <v>0.912</v>
+        <v>0.92492</v>
       </c>
       <c r="M2" t="n">
-        <v>0.309</v>
+        <v>0.30891</v>
       </c>
       <c r="N2" t="n">
-        <v>0.233</v>
+        <v>0.22396</v>
       </c>
       <c r="O2" t="n">
-        <v>0.168</v>
+        <v>0.15141</v>
       </c>
       <c r="P2" t="n">
-        <v>0.376</v>
+        <v>0.43003</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1543,13 +1543,13 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.123</v>
+        <v>0.11601</v>
       </c>
       <c r="X2" t="n">
-        <v>0.488</v>
+        <v>0.32716</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07051</v>
       </c>
     </row>
     <row r="3">
@@ -1559,49 +1559,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.311</v>
+        <v>0.42392</v>
       </c>
       <c r="C3" t="n">
-        <v>0.39</v>
+        <v>0.46805</v>
       </c>
       <c r="D3" t="n">
-        <v>0.258</v>
+        <v>0.38739</v>
       </c>
       <c r="E3" t="n">
-        <v>0.522</v>
+        <v>0.6244499999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.401</v>
+        <v>0.54228</v>
       </c>
       <c r="G3" t="n">
-        <v>0.75</v>
+        <v>0.73598</v>
       </c>
       <c r="H3" t="n">
-        <v>0.611</v>
+        <v>0.5412</v>
       </c>
       <c r="I3" t="n">
-        <v>0.544</v>
+        <v>0.44296</v>
       </c>
       <c r="J3" t="n">
-        <v>0.695</v>
+        <v>0.69543</v>
       </c>
       <c r="K3" t="n">
-        <v>0.442</v>
+        <v>0.44379</v>
       </c>
       <c r="L3" t="n">
-        <v>0.887</v>
+        <v>0.90301</v>
       </c>
       <c r="M3" t="n">
-        <v>0.294</v>
+        <v>0.29419</v>
       </c>
       <c r="N3" t="n">
-        <v>0.165</v>
+        <v>0.20911</v>
       </c>
       <c r="O3" t="n">
-        <v>0.117</v>
+        <v>0.14309</v>
       </c>
       <c r="P3" t="n">
-        <v>0.28</v>
+        <v>0.38823</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1622,13 +1622,13 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.08</v>
+        <v>0.07983999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>0.444</v>
+        <v>0.44444</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.044</v>
+        <v>0.04386</v>
       </c>
     </row>
     <row r="4">
@@ -1638,49 +1638,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.346</v>
+        <v>0.46933</v>
       </c>
       <c r="C4" t="n">
-        <v>0.434</v>
+        <v>0.52089</v>
       </c>
       <c r="D4" t="n">
-        <v>0.288</v>
+        <v>0.42705</v>
       </c>
       <c r="E4" t="n">
-        <v>0.661</v>
+        <v>0.80441</v>
       </c>
       <c r="F4" t="n">
-        <v>0.526</v>
+        <v>0.72701</v>
       </c>
       <c r="G4" t="n">
-        <v>0.889</v>
+        <v>0.90024</v>
       </c>
       <c r="H4" t="n">
-        <v>0.488</v>
+        <v>0.48822</v>
       </c>
       <c r="I4" t="n">
-        <v>0.454</v>
+        <v>0.45433</v>
       </c>
       <c r="J4" t="n">
-        <v>0.528</v>
+        <v>0.52757</v>
       </c>
       <c r="K4" t="n">
-        <v>0.34</v>
+        <v>0.35217</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.79488</v>
       </c>
       <c r="M4" t="n">
-        <v>0.226</v>
+        <v>0.22619</v>
       </c>
       <c r="N4" t="n">
-        <v>0.22</v>
+        <v>0.21949</v>
       </c>
       <c r="O4" t="n">
-        <v>0.16</v>
+        <v>0.15227</v>
       </c>
       <c r="P4" t="n">
-        <v>0.349</v>
+        <v>0.39299</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1701,13 +1701,13 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.32</v>
+        <v>0.29545</v>
       </c>
       <c r="X4" t="n">
-        <v>0.723</v>
+        <v>0.52366</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.206</v>
+        <v>0.20577</v>
       </c>
     </row>
     <row r="5">
@@ -1717,49 +1717,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.316</v>
+        <v>0.45245</v>
       </c>
       <c r="C5" t="n">
-        <v>0.434</v>
+        <v>0.52127</v>
       </c>
       <c r="D5" t="n">
-        <v>0.248</v>
+        <v>0.39969</v>
       </c>
       <c r="E5" t="n">
-        <v>0.548</v>
+        <v>0.75344</v>
       </c>
       <c r="F5" t="n">
-        <v>0.401</v>
+        <v>0.65959</v>
       </c>
       <c r="G5" t="n">
-        <v>0.865</v>
+        <v>0.87843</v>
       </c>
       <c r="H5" t="n">
-        <v>0.383</v>
+        <v>0.38301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.394</v>
+        <v>0.3937</v>
       </c>
       <c r="J5" t="n">
-        <v>0.373</v>
+        <v>0.37288</v>
       </c>
       <c r="K5" t="n">
-        <v>0.351</v>
+        <v>0.34588</v>
       </c>
       <c r="L5" t="n">
-        <v>0.887</v>
+        <v>0.83027</v>
       </c>
       <c r="M5" t="n">
-        <v>0.218</v>
+        <v>0.21844</v>
       </c>
       <c r="N5" t="n">
-        <v>0.145</v>
+        <v>0.18447</v>
       </c>
       <c r="O5" t="n">
-        <v>0.101</v>
+        <v>0.12468</v>
       </c>
       <c r="P5" t="n">
-        <v>0.256</v>
+        <v>0.35447</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1771,22 +1771,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001</v>
+        <v>0.00151</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.00076</v>
       </c>
       <c r="W5" t="n">
-        <v>0.305</v>
+        <v>0.2867</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.196</v>
+        <v>0.19633</v>
       </c>
     </row>
   </sheetData>
@@ -1937,49 +1937,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.328</v>
+        <v>0.41158</v>
       </c>
       <c r="C2" t="n">
-        <v>0.394</v>
+        <v>0.42653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.281</v>
+        <v>0.39765</v>
       </c>
       <c r="E2" t="n">
-        <v>0.553</v>
+        <v>0.6167</v>
       </c>
       <c r="F2" t="n">
-        <v>0.437</v>
+        <v>0.53893</v>
       </c>
       <c r="G2" t="n">
-        <v>0.753</v>
+        <v>0.7206900000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.657</v>
+        <v>0.52494</v>
       </c>
       <c r="I2" t="n">
-        <v>0.594</v>
+        <v>0.40819</v>
       </c>
       <c r="J2" t="n">
-        <v>0.735</v>
+        <v>0.73524</v>
       </c>
       <c r="K2" t="n">
-        <v>0.438</v>
+        <v>0.43982</v>
       </c>
       <c r="L2" t="n">
-        <v>0.912</v>
+        <v>0.92492</v>
       </c>
       <c r="M2" t="n">
-        <v>0.289</v>
+        <v>0.28851</v>
       </c>
       <c r="N2" t="n">
-        <v>0.217</v>
+        <v>0.19967</v>
       </c>
       <c r="O2" t="n">
-        <v>0.153</v>
+        <v>0.13002</v>
       </c>
       <c r="P2" t="n">
-        <v>0.376</v>
+        <v>0.43003</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -2000,13 +2000,13 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.123</v>
+        <v>0.11601</v>
       </c>
       <c r="X2" t="n">
-        <v>0.488</v>
+        <v>0.32716</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07051</v>
       </c>
     </row>
     <row r="3">
@@ -2016,49 +2016,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.289</v>
+        <v>0.41332</v>
       </c>
       <c r="C3" t="n">
-        <v>0.386</v>
+        <v>0.46278</v>
       </c>
       <c r="D3" t="n">
-        <v>0.231</v>
+        <v>0.37342</v>
       </c>
       <c r="E3" t="n">
-        <v>0.521</v>
+        <v>0.62166</v>
       </c>
       <c r="F3" t="n">
-        <v>0.399</v>
+        <v>0.53807</v>
       </c>
       <c r="G3" t="n">
-        <v>0.75</v>
+        <v>0.73598</v>
       </c>
       <c r="H3" t="n">
-        <v>0.556</v>
+        <v>0.49752</v>
       </c>
       <c r="I3" t="n">
-        <v>0.544</v>
+        <v>0.44296</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.56741</v>
       </c>
       <c r="K3" t="n">
-        <v>0.426</v>
+        <v>0.42812</v>
       </c>
       <c r="L3" t="n">
-        <v>0.887</v>
+        <v>0.90301</v>
       </c>
       <c r="M3" t="n">
-        <v>0.281</v>
+        <v>0.28057</v>
       </c>
       <c r="N3" t="n">
-        <v>0.152</v>
+        <v>0.1923</v>
       </c>
       <c r="O3" t="n">
-        <v>0.104</v>
+        <v>0.1278</v>
       </c>
       <c r="P3" t="n">
-        <v>0.28</v>
+        <v>0.38823</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -2079,13 +2079,13 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.011</v>
+        <v>0.01128</v>
       </c>
       <c r="X3" t="n">
-        <v>0.444</v>
+        <v>0.44444</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.006</v>
+        <v>0.00571</v>
       </c>
     </row>
     <row r="4">
@@ -2095,49 +2095,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.342</v>
+        <v>0.46036</v>
       </c>
       <c r="C4" t="n">
-        <v>0.428</v>
+        <v>0.51181</v>
       </c>
       <c r="D4" t="n">
-        <v>0.285</v>
+        <v>0.41831</v>
       </c>
       <c r="E4" t="n">
-        <v>0.655</v>
+        <v>0.78873</v>
       </c>
       <c r="F4" t="n">
-        <v>0.524</v>
+        <v>0.72273</v>
       </c>
       <c r="G4" t="n">
-        <v>0.872</v>
+        <v>0.86799</v>
       </c>
       <c r="H4" t="n">
-        <v>0.488</v>
+        <v>0.48822</v>
       </c>
       <c r="I4" t="n">
-        <v>0.454</v>
+        <v>0.45433</v>
       </c>
       <c r="J4" t="n">
-        <v>0.528</v>
+        <v>0.52757</v>
       </c>
       <c r="K4" t="n">
-        <v>0.34</v>
+        <v>0.35217</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.79488</v>
       </c>
       <c r="M4" t="n">
-        <v>0.226</v>
+        <v>0.22619</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2</v>
+        <v>0.18788</v>
       </c>
       <c r="O4" t="n">
-        <v>0.14</v>
+        <v>0.12345</v>
       </c>
       <c r="P4" t="n">
-        <v>0.349</v>
+        <v>0.39299</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -2158,13 +2158,13 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.32</v>
+        <v>0.29545</v>
       </c>
       <c r="X4" t="n">
-        <v>0.723</v>
+        <v>0.52366</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.206</v>
+        <v>0.20577</v>
       </c>
     </row>
     <row r="5">
@@ -2174,49 +2174,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.315</v>
+        <v>0.45004</v>
       </c>
       <c r="C5" t="n">
-        <v>0.429</v>
+        <v>0.5149</v>
       </c>
       <c r="D5" t="n">
-        <v>0.248</v>
+        <v>0.39969</v>
       </c>
       <c r="E5" t="n">
-        <v>0.546</v>
+        <v>0.75076</v>
       </c>
       <c r="F5" t="n">
-        <v>0.399</v>
+        <v>0.65549</v>
       </c>
       <c r="G5" t="n">
-        <v>0.865</v>
+        <v>0.87843</v>
       </c>
       <c r="H5" t="n">
-        <v>0.383</v>
+        <v>0.38301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.394</v>
+        <v>0.3937</v>
       </c>
       <c r="J5" t="n">
-        <v>0.373</v>
+        <v>0.37288</v>
       </c>
       <c r="K5" t="n">
-        <v>0.351</v>
+        <v>0.34588</v>
       </c>
       <c r="L5" t="n">
-        <v>0.887</v>
+        <v>0.83027</v>
       </c>
       <c r="M5" t="n">
-        <v>0.218</v>
+        <v>0.21844</v>
       </c>
       <c r="N5" t="n">
-        <v>0.124</v>
+        <v>0.16118</v>
       </c>
       <c r="O5" t="n">
-        <v>0.082</v>
+        <v>0.1043</v>
       </c>
       <c r="P5" t="n">
-        <v>0.256</v>
+        <v>0.35447</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2228,22 +2228,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001</v>
+        <v>0.00151</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.00076</v>
       </c>
       <c r="W5" t="n">
-        <v>0.305</v>
+        <v>0.2867</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.196</v>
+        <v>0.19633</v>
       </c>
     </row>
   </sheetData>
@@ -2394,49 +2394,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.374</v>
+        <v>0.45596</v>
       </c>
       <c r="C2" t="n">
-        <v>0.398</v>
+        <v>0.43328</v>
       </c>
       <c r="D2" t="n">
-        <v>0.356</v>
+        <v>0.48506</v>
       </c>
       <c r="E2" t="n">
-        <v>0.571</v>
+        <v>0.6432099999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.819</v>
+        <v>0.79082</v>
       </c>
       <c r="G2" t="n">
-        <v>0.439</v>
+        <v>0.54249</v>
       </c>
       <c r="H2" t="n">
-        <v>0.707</v>
+        <v>0.55636</v>
       </c>
       <c r="I2" t="n">
-        <v>0.883</v>
+        <v>0.88296</v>
       </c>
       <c r="J2" t="n">
-        <v>0.594</v>
+        <v>0.40819</v>
       </c>
       <c r="K2" t="n">
-        <v>0.662</v>
+        <v>0.66564</v>
       </c>
       <c r="L2" t="n">
-        <v>0.544</v>
+        <v>0.54419</v>
       </c>
       <c r="M2" t="n">
-        <v>0.912</v>
+        <v>0.92492</v>
       </c>
       <c r="N2" t="n">
-        <v>0.244</v>
+        <v>0.22815</v>
       </c>
       <c r="O2" t="n">
-        <v>0.459</v>
+        <v>0.48662</v>
       </c>
       <c r="P2" t="n">
-        <v>0.167</v>
+        <v>0.14927</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -2457,13 +2457,13 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.215</v>
+        <v>0.19257</v>
       </c>
       <c r="X2" t="n">
-        <v>0.143</v>
+        <v>0.14279</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.488</v>
+        <v>0.32716</v>
       </c>
     </row>
     <row r="3">
@@ -2473,49 +2473,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.354</v>
+        <v>0.46605</v>
       </c>
       <c r="C3" t="n">
-        <v>0.389</v>
+        <v>0.46753</v>
       </c>
       <c r="D3" t="n">
-        <v>0.33</v>
+        <v>0.46924</v>
       </c>
       <c r="E3" t="n">
-        <v>0.537</v>
+        <v>0.64191</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.78832</v>
       </c>
       <c r="G3" t="n">
-        <v>0.401</v>
+        <v>0.54186</v>
       </c>
       <c r="H3" t="n">
-        <v>0.659</v>
+        <v>0.57879</v>
       </c>
       <c r="I3" t="n">
-        <v>0.853</v>
+        <v>0.85293</v>
       </c>
       <c r="J3" t="n">
-        <v>0.544</v>
+        <v>0.44296</v>
       </c>
       <c r="K3" t="n">
-        <v>0.649</v>
+        <v>0.6531400000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.538</v>
+        <v>0.53776</v>
       </c>
       <c r="M3" t="n">
-        <v>0.887</v>
+        <v>0.90301</v>
       </c>
       <c r="N3" t="n">
-        <v>0.17</v>
+        <v>0.21431</v>
       </c>
       <c r="O3" t="n">
-        <v>0.321</v>
+        <v>0.44423</v>
       </c>
       <c r="P3" t="n">
-        <v>0.116</v>
+        <v>0.14156</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -2536,13 +2536,13 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.18</v>
+        <v>0.18023</v>
       </c>
       <c r="X3" t="n">
-        <v>0.122</v>
+        <v>0.12225</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.444</v>
+        <v>0.44444</v>
       </c>
     </row>
     <row r="4">
@@ -2552,49 +2552,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.389</v>
+        <v>0.50528</v>
       </c>
       <c r="C4" t="n">
-        <v>0.433</v>
+        <v>0.51998</v>
       </c>
       <c r="D4" t="n">
-        <v>0.358</v>
+        <v>0.49455</v>
       </c>
       <c r="E4" t="n">
-        <v>0.676</v>
+        <v>0.82324</v>
       </c>
       <c r="F4" t="n">
-        <v>0.948</v>
+        <v>0.95081</v>
       </c>
       <c r="G4" t="n">
-        <v>0.526</v>
+        <v>0.72658</v>
       </c>
       <c r="H4" t="n">
-        <v>0.519</v>
+        <v>0.5191</v>
       </c>
       <c r="I4" t="n">
-        <v>0.612</v>
+        <v>0.61193</v>
       </c>
       <c r="J4" t="n">
-        <v>0.454</v>
+        <v>0.45433</v>
       </c>
       <c r="K4" t="n">
-        <v>0.488</v>
+        <v>0.5154300000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.398</v>
+        <v>0.39834</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.79488</v>
       </c>
       <c r="N4" t="n">
-        <v>0.229</v>
+        <v>0.2219</v>
       </c>
       <c r="O4" t="n">
-        <v>0.419</v>
+        <v>0.43257</v>
       </c>
       <c r="P4" t="n">
-        <v>0.158</v>
+        <v>0.14939</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -2615,13 +2615,13 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.452</v>
+        <v>0.4012</v>
       </c>
       <c r="X4" t="n">
-        <v>0.344</v>
+        <v>0.34395</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.723</v>
+        <v>0.52366</v>
       </c>
     </row>
     <row r="5">
@@ -2631,49 +2631,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.364</v>
+        <v>0.49361</v>
       </c>
       <c r="C5" t="n">
-        <v>0.433</v>
+        <v>0.52063</v>
       </c>
       <c r="D5" t="n">
-        <v>0.32</v>
+        <v>0.47282</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.77668</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9467</v>
       </c>
       <c r="G5" t="n">
-        <v>0.401</v>
+        <v>0.65918</v>
       </c>
       <c r="H5" t="n">
-        <v>0.423</v>
+        <v>0.42272</v>
       </c>
       <c r="I5" t="n">
-        <v>0.465</v>
+        <v>0.46518</v>
       </c>
       <c r="J5" t="n">
-        <v>0.394</v>
+        <v>0.3937</v>
       </c>
       <c r="K5" t="n">
-        <v>0.509</v>
+        <v>0.49847</v>
       </c>
       <c r="L5" t="n">
-        <v>0.368</v>
+        <v>0.36785</v>
       </c>
       <c r="M5" t="n">
-        <v>0.887</v>
+        <v>0.83027</v>
       </c>
       <c r="N5" t="n">
-        <v>0.147</v>
+        <v>0.18669</v>
       </c>
       <c r="O5" t="n">
-        <v>0.283</v>
+        <v>0.39216</v>
       </c>
       <c r="P5" t="n">
-        <v>0.099</v>
+        <v>0.12264</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2685,22 +2685,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05</v>
+        <v>0.07814</v>
       </c>
       <c r="U5" t="n">
-        <v>0.027</v>
+        <v>0.04273</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.437</v>
+        <v>0.39706</v>
       </c>
       <c r="X5" t="n">
-        <v>0.337</v>
+        <v>0.33717</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.53125</v>
       </c>
     </row>
   </sheetData>
